--- a/benchmark-dataset/tables/pockets.xlsx
+++ b/benchmark-dataset/tables/pockets.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1299,17 +1299,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>zhang2015</t>
+          <t>kimura2019</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The role of serotonin 5-HT2A receptors in memory and cognition</t>
+          <t>Structures of the 5-HT2A receptor in complex with the antipsychotics risperidone and zotepine</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10.3389/fphar.2015.00225</t>
+          <t>10.1038/s41594-018-0180-z</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1319,12 +1319,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ligand binding pocket</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Risperidone and zotepine exhibit high affinities not only for 5-HT2AR and D2R, but also for 5-HT2CR, the dopamine D3 and D4 receptors, α1A-adrenergic receptors, and H1R. The residues involved in the binding of risperidone or zotepine in 5-HT2AR are highly conserved in aminergic receptors, particularly on the intracellular side of the conserved salt bridge.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Zotepine, Risperidone</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>5-HT2A</t>
@@ -1334,64 +1346,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kimura2019</t>
+          <t>lugo1990</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Structures of the 5-HT2A receptor in complex with the antipsychotics risperidone and zotepine</t>
+          <t>Tyrosine Kinase Activity and Transformation Potency of bcr-abl Oncogene Products</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10.1038/s41594-018-0180-z</t>
+          <t>10.1126/science.2408149</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5-hydroxytryptamine receptor 2A</t>
+          <t>Tyrosine-protein kinase ABL1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Ligand binding pocket</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Risperidone and zotepine exhibit high affinities not only for 5-HT2AR and D2R, but also for 5-HT2CR, the dopamine D3 and D4 receptors, α1A-adrenergic receptors, and H1R. The residues involved in the binding of risperidone or zotepine in 5-HT2AR are highly conserved in aminergic receptors, particularly on the intracellular side of the conserved salt bridge.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Zotepine, Risperidone</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5-HT2A</t>
+          <t>ABL1_kinase</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>lugo1990</t>
+          <t>simpson2019</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tyrosine Kinase Activity and Transformation Potency of bcr-abl Oncogene Products</t>
+          <t>Identification and Optimization of Novel Small c-Abl Kinase Activators Using Fragment and HTS Methodologies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>10.1126/science.2408149</t>
+          <t>10.1021/acs.jmedchem.8b01872</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1401,12 +1401,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Myristoyl binding site</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Allosteric inhibitors of c-Abl kinase, also active against BCR-Abl, bind at the myristoyl pocket, stabilizing interaction with helix αI′ and mimicking the autoinhibited conformation of c-Abl. Concurrently, our group have previously described the discovery of a small molecule activator of c-Abl kinase, which binds at the same pocket, displacing the myristoyl latch and leading to a cellular activation</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>DPH, Aminothiazoles</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>ABL1_kinase</t>
@@ -1416,17 +1428,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>simpson2019</t>
+          <t>jingsong2011</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Identification and Optimization of Novel Small c-Abl Kinase Activators Using Fragment and HTS Methodologies</t>
+          <t>Discovery and Characterization of a CellPermeable, Small-Molecule c-Abl Kinase Activator that Binds to the Myristoyl Binding Site</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>10.1021/acs.jmedchem.8b01872</t>
+          <t>10.1016/j.chembiol.2010.12.013</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1446,12 +1458,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Allosteric inhibitors of c-Abl kinase, also active against BCR-Abl, bind at the myristoyl pocket, stabilizing interaction with helix αI′ and mimicking the autoinhibited conformation of c-Abl. Concurrently, our group have previously described the discovery of a small molecule activator of c-Abl kinase, which binds at the same pocket, displacing the myristoyl latch and leading to a cellular activation</t>
+          <t>Based on the crystal structure, the N-terminal myristoyl group of c-Abl binds to the myristoyl binding site on the C-lobe of the kinase domain and this binding helps maintain the inactive conformation of c-Ab. The above FP binding data strongly suggest that DPH binds to the myristoyl binding site of c-Abl.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>DPH, Aminothiazoles</t>
+          <t>R-DPH</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1463,17 +1475,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>jingsong2011</t>
+          <t>weisberg2006</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Discovery and Characterization of a CellPermeable, Small-Molecule c-Abl Kinase Activator that Binds to the Myristoyl Binding Site</t>
+          <t>AMN107 (nilotinib): a novel and selective inhibitor of BCR-ABL</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10.1016/j.chembiol.2010.12.013</t>
+          <t>10.1038/sj.bjc.6603170</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1488,17 +1500,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Myristoyl binding site</t>
+          <t>ATP binding site</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Based on the crystal structure, the N-terminal myristoyl group of c-Abl binds to the myristoyl binding site on the C-lobe of the kinase domain and this binding helps maintain the inactive conformation of c-Ab. The above FP binding data strongly suggest that DPH binds to the myristoyl binding site of c-Abl.</t>
+          <t>The novel, selective BCRABL inhibitor, AMN107, was designed to fit into the ATP-binding site of the BCR-ABL protein with higher affinity than imatinib.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>R-DPH</t>
+          <t>AMN107 (nilotinib)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1510,69 +1522,57 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>weisberg2006</t>
+          <t>perera2013</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AMN107 (nilotinib): a novel and selective inhibitor of BCR-ABL</t>
+          <t>Mechanism for priming DNA synthesis by yeast DNA Polymerase α</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10.1038/sj.bjc.6603170</t>
+          <t>10.7554/eLife.00482</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tyrosine-protein kinase ABL1</t>
+          <t>DNA polymerase alpha</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ATP binding site</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>The novel, selective BCRABL inhibitor, AMN107, was designed to fit into the ATP-binding site of the BCR-ABL protein with higher affinity than imatinib.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>AMN107 (nilotinib)</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ABL1_kinase</t>
+          <t>Polymerase_alpha_human</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>jabbour2016</t>
+          <t>srivastava2003</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chronic myelomonocytic leukemia: 2016 update on diagnosis, risk stratification, and management</t>
+          <t>Replicative enzymes, DNA polymerase alpha (pol alpha), and in vitro ageing</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>10.1002/ajh.24396</t>
+          <t>10.1016/j.exger.2003.09.008</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tyrosine-protein kinase ABL1</t>
+          <t>DNA polymerase alpha</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1585,169 +1585,217 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ABL1_kinase</t>
+          <t>Polymerase_alpha_human</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>wylie2017</t>
+          <t>baranovskiy2014</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The allosteric inhibitor ABL001 enables dual targeting of BCR–ABL1</t>
+          <t>Structural basis for inhibition of DNA replication by aphidicolin</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>10.1038/nature21702</t>
+          <t>10.1093/nar/gku1209</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tyrosine-protein kinase ABL1</t>
+          <t>DNA polymerase alpha</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>dNTP-binding site</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The dNTP-binding site of human Pol alpha is located at the junction between the palm and the fingers. Upon dNTP binding, the latter subdomain is able to change its conformation from open to the closed one, which results in stabilization of the precatalytic ternary complex Pol/template: primer/dNTP. This structure catches the transient step of dNTP binding followed by fingers closing and phosphodiester bond formation. It revealed that fingers interact with dNTP even in the open conformation. </t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Aphidicolin</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ABL1_kinase</t>
+          <t>Polymerase_alpha_human</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nagar2006</t>
+          <t>baranovskiy2018</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Organization of the SH3-SH2 unit in active and inactive forms of the c-Abl tyrosine kinase</t>
+          <t>Activity and fidelity of human DNA polymerase  depend on primer structure</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10.1016/j.molcel.2006.01.035</t>
+          <t>10.1074/jbc.RA117.001074</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tyrosine-protein kinase ABL1</t>
+          <t>DNA polymerase alpha</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>dNTP-binding site</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>The dNTP-binding site of B-family Pols is located at the junction between the palm and the fingers (Fig. 4A). Upon dNTP binding, the latter subdomain is able to change its conformation from open to the closed one, which results in stabilization of the precatalytic ternary complex Pol/template: primer/dNTP.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>dNTP</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ABL1_kinase</t>
+          <t>Polymerase_alpha_human</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>perera2013</t>
+          <t>murphy2014</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mechanism for priming DNA synthesis by yeast DNA Polymerase α</t>
+          <t>Insights into the evolution of divergent nucleotide-binding mechanisms among pseudokinases revealed by crystal structures of human and mouse MLKL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>10.7554/eLife.00482</t>
+          <t>10.1042/BJ20131270</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DNA polymerase alpha</t>
+          <t>Mixed lineage kinase domain-like protein</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ATP-binding site</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pseudoactive site of the human MLKL. ATP is readily accommodated in the pseudoactive site of human MLKL, with the only potential hindrance arising from the packing of the side chain from the glycine-rich loop residue, Arg210. DFG motif of PKA is replaced by GFE in human MLKL. the position of the human MLKL ‘catalytic’ loop differs markedly from that of PKA. The human MLKL sequence lacks the catalytic aspartic acid usually present within the HRD motif of conventional protein kinases (YRD in PKA) and instead contains HGK. Of particular note, the human MLKL pseudoactive site is markedly different from that of mouse MLKL.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ADP, AMP-PNP, GTP, AMP</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Polymerase_alpha_human</t>
+          <t>MLKL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>srivastava2003</t>
+          <t>ma2017</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Replicative enzymes, DNA polymerase alpha (pol alpha), and in vitro ageing</t>
+          <t>ATP-Competitive MLKL Binders Have No Functional Impact on Necroptosis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>10.1016/j.exger.2003.09.008</t>
+          <t>10.1371/journal.pone.0165983</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DNA polymerase alpha</t>
+          <t>Mixed lineage kinase domain-like protein</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ATP-binding site</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>The co-crystal structure showed that cpd 1 binds in the ATP binding site of MLKL by making two hydrogen bond interactions between the backbone amide and carbonyl of the hinge and the amino pyrimidine of the compound.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>cpd1-4</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Polymerase_alpha_human</t>
+          <t>MLKL</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baranovskiy2014</t>
+          <t>kruse2012</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Structural basis for inhibition of DNA replication by aphidicolin</t>
+          <t>Structure and Dynamics of the M3 Muscarinic Acetylcholine Receptor</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10.1093/nar/gku1209</t>
+          <t>10.1038/nature10867</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DNA polymerase alpha</t>
+          <t>Muscarinic acetylcholine receptor M3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1757,91 +1805,79 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>dNTP-binding site</t>
+          <t>Orthosteric binding site</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">The dNTP-binding site of human Pol alpha is located at the junction between the palm and the fingers. Upon dNTP binding, the latter subdomain is able to change its conformation from open to the closed one, which results in stabilization of the precatalytic ternary complex Pol/template: primer/dNTP. This structure catches the transient step of dNTP binding followed by fingers closing and phosphodiester bond formation. It revealed that fingers interact with dNTP even in the open conformation. </t>
+          <t>In the M3 receptor, as in M2, the ligand is deeply buried within the TM receptor core and covered by a lid of three conserved tyrosines: Y148, Y506, and Y529.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Aphidicolin</t>
+          <t>QNB</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Polymerase_alpha_human</t>
+          <t>GPCR_m2-m3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>baranovskiy2018</t>
+          <t>ockenga2013</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Activity and fidelity of human DNA polymerase  depend on primer structure</t>
+          <t>Non-Neuronal Functions of the M2 Muscarinic Acetylcholine Receptor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>10.1074/jbc.RA117.001074</t>
+          <t>10.3390/genes4020171</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DNA polymerase alpha</t>
+          <t>Muscarinic acetylcholine receptor M2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>dNTP-binding site</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>The dNTP-binding site of B-family Pols is located at the junction between the palm and the fingers (Fig. 4A). Upon dNTP binding, the latter subdomain is able to change its conformation from open to the closed one, which results in stabilization of the precatalytic ternary complex Pol/template: primer/dNTP.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>dNTP</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Polymerase_alpha_human</t>
+          <t>GPCR_m2-m3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>murphy2014</t>
+          <t>kruse2015</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Insights into the evolution of divergent nucleotide-binding mechanisms among pseudokinases revealed by crystal structures of human and mouse MLKL</t>
+          <t>Muscarinic acetylcholine receptors: novel opportunities for drug development</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10.1042/BJ20131270</t>
+          <t>10.1038/nrd4295</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mixed lineage kinase domain-like protein</t>
+          <t>Muscarinic acetylcholine receptor M2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1851,44 +1887,44 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ATP-binding site</t>
+          <t>Extracellular vestibule</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudoactive site of the human MLKL. ATP is readily accommodated in the pseudoactive site of human MLKL, with the only potential hindrance arising from the packing of the side chain from the glycine-rich loop residue, Arg210. DFG motif of PKA is replaced by GFE in human MLKL. the position of the human MLKL ‘catalytic’ loop differs markedly from that of PKA. The human MLKL sequence lacks the catalytic aspartic acid usually present within the HRD motif of conventional protein kinases (YRD in PKA) and instead contains HGK. Of particular note, the human MLKL pseudoactive site is markedly different from that of mouse MLKL.</t>
+          <t>Part of the large, solvent-accesible cavity, located at the upper portion of this cavity and termed extracellular verstibule. It is lined with residues that have been implicated in the binding of allosteric modulators.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ADP, AMP-PNP, GTP, AMP</t>
+          <t>LY2119620</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>MLKL</t>
+          <t>GPCR_m2-m3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ma2017</t>
+          <t>kruse2015</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ATP-Competitive MLKL Binders Have No Functional Impact on Necroptosis</t>
+          <t>Muscarinic acetylcholine receptors: novel opportunities for drug development</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>10.1371/journal.pone.0165983</t>
+          <t>10.1038/nrd4295</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mixed lineage kinase domain-like protein</t>
+          <t>Muscarinic acetylcholine receptor M2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1898,39 +1934,39 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ATP-binding site</t>
+          <t>Orthosteric binding site</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>The co-crystal structure showed that cpd 1 binds in the ATP binding site of MLKL by making two hydrogen bond interactions between the backbone amide and carbonyl of the hinge and the amino pyrimidine of the compound.</t>
+          <t>In the active state of the M2 receptor, the small orthosteric agonist iperoxo engages Asp1033.32 with its cationic head group, whereas the polar isoxazoline tail contacts Asn4046.52 with a single hydrogen bond, paralleling the interactions of the inactive receptor with the antagonist QNB (FIG. 4c).</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>cpd1-4</t>
+          <t>Iperoxo</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>MLKL</t>
+          <t>GPCR_m2-m3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kruse2012</t>
+          <t>tanahashi2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Structure and Dynamics of the M3 Muscarinic Acetylcholine Receptor</t>
+          <t>Functions of Muscarinic Receptor Subtypes in Gastrointestinal Smooth Muscle: A Review of Studies with Receptor-Knockout Mice</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>10.1038/nature10867</t>
+          <t>10.3390/ijms22020926</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1940,189 +1976,13 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Orthosteric binding site</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>In the M3 receptor, as in M2, the ligand is deeply buried within the TM receptor core and covered by a lid of three conserved tyrosines: Y148, Y506, and Y529.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>QNB</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
-        <is>
-          <t>GPCR_m2-m3</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ockenga2013</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Non-Neuronal Functions of the M2 Muscarinic Acetylcholine Receptor</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>10.3390/genes4020171</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Muscarinic acetylcholine receptor M2</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>GPCR_m2-m3</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>kruse2015</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Muscarinic acetylcholine receptors: novel opportunities for drug development</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>10.1038/nrd4295</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Muscarinic acetylcholine receptor M2</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Extracellular vestibule</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Part of the large, solvent-accesible cavity, located at the upper portion of this cavity and termed extracellular verstibule. It is lined with residues that have been implicated in the binding of allosteric modulators.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>LY2119620</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>GPCR_m2-m3</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>kruse2015</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Muscarinic acetylcholine receptors: novel opportunities for drug development</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>10.1038/nrd4295</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Muscarinic acetylcholine receptor M2</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Orthosteric binding site</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>In the active state of the M2 receptor, the small orthosteric agonist iperoxo engages Asp1033.32 with its cationic head group, whereas the polar isoxazoline tail contacts Asn4046.52 with a single hydrogen bond, paralleling the interactions of the inactive receptor with the antagonist QNB (FIG. 4c).</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Iperoxo</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>GPCR_m2-m3</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>tanahashi2021</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Functions of Muscarinic Receptor Subtypes in Gastrointestinal Smooth Muscle: A Review of Studies with Receptor-Knockout Mice</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>10.3390/ijms22020926</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Muscarinic acetylcholine receptor M3</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
         <is>
           <t>GPCR_m2-m3</t>
         </is>
